--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0003T0006Z000C1N4_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0003T0006Z000C1N4_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>58.23656192361747</v>
+        <v>9.463441312587838</v>
       </c>
       <c r="D2" t="n">
-        <v>21.52873531254351</v>
+        <v>3.498419488288321</v>
       </c>
       <c r="E2" t="n">
-        <v>16.24112554593532</v>
+        <v>2.63918290121449</v>
       </c>
       <c r="F2" t="n">
-        <v>16.50123754975794</v>
+        <v>2.681451101835666</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>61.91960862513606</v>
+        <v>10.06193640158461</v>
       </c>
       <c r="D3" t="n">
-        <v>35.32445068166231</v>
+        <v>5.740223235770126</v>
       </c>
       <c r="E3" t="n">
-        <v>16.24112554593532</v>
+        <v>2.63918290121449</v>
       </c>
       <c r="F3" t="n">
-        <v>16.50123754975794</v>
+        <v>2.681451101835666</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>63.89051687321657</v>
+        <v>10.38220899189769</v>
       </c>
       <c r="D4" t="n">
-        <v>43.02179692592512</v>
+        <v>6.991042000462832</v>
       </c>
       <c r="E4" t="n">
-        <v>16.24112554593532</v>
+        <v>2.63918290121449</v>
       </c>
       <c r="F4" t="n">
-        <v>16.50123754975794</v>
+        <v>2.681451101835666</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>65.31440576858593</v>
+        <v>10.61359093739521</v>
       </c>
       <c r="D5" t="n">
-        <v>58.87158106267702</v>
+        <v>9.566631922685016</v>
       </c>
       <c r="E5" t="n">
-        <v>16.24112554593532</v>
+        <v>2.63918290121449</v>
       </c>
       <c r="F5" t="n">
-        <v>16.50123754975794</v>
+        <v>2.681451101835666</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>50.3656837677651</v>
+        <v>8.184423612261829</v>
       </c>
       <c r="D6" t="n">
-        <v>24.91905010760309</v>
+        <v>4.049345642485503</v>
       </c>
       <c r="E6" t="n">
-        <v>16.24112554593532</v>
+        <v>2.63918290121449</v>
       </c>
       <c r="F6" t="n">
-        <v>16.50123754975794</v>
+        <v>2.681451101835666</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>66.98337728613295</v>
+        <v>10.8847988089966</v>
       </c>
       <c r="D7" t="n">
-        <v>64.62658825746982</v>
+        <v>10.50182059183885</v>
       </c>
       <c r="E7" t="n">
-        <v>16.24112554593532</v>
+        <v>2.63918290121449</v>
       </c>
       <c r="F7" t="n">
-        <v>16.50123754975794</v>
+        <v>2.681451101835666</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>28.85396170327325</v>
+        <v>4.688768776781903</v>
       </c>
       <c r="D8" t="n">
-        <v>29.61985036052297</v>
+        <v>4.813225683584983</v>
       </c>
       <c r="E8" t="n">
-        <v>16.24112554593532</v>
+        <v>2.63918290121449</v>
       </c>
       <c r="F8" t="n">
-        <v>16.50123754975794</v>
+        <v>2.681451101835666</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>18.20797629388634</v>
+        <v>2.958796147756531</v>
       </c>
       <c r="D9" t="n">
-        <v>16.64037903940526</v>
+        <v>2.704061593903355</v>
       </c>
       <c r="E9" t="n">
-        <v>16.24112554593532</v>
+        <v>2.63918290121449</v>
       </c>
       <c r="F9" t="n">
-        <v>16.50123754975794</v>
+        <v>2.681451101835666</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>43.26061705124328</v>
+        <v>7.029850270827033</v>
       </c>
       <c r="D10" t="n">
-        <v>53.10657881772825</v>
+        <v>8.629819057880841</v>
       </c>
       <c r="E10" t="n">
-        <v>16.24112554593532</v>
+        <v>2.63918290121449</v>
       </c>
       <c r="F10" t="n">
-        <v>16.50123754975794</v>
+        <v>2.681451101835666</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>23.74323080057389</v>
+        <v>3.858275005093258</v>
       </c>
       <c r="D11" t="n">
-        <v>21.70408923018449</v>
+        <v>3.526914499904979</v>
       </c>
       <c r="E11" t="n">
-        <v>16.24112554593532</v>
+        <v>2.63918290121449</v>
       </c>
       <c r="F11" t="n">
-        <v>16.50123754975794</v>
+        <v>2.681451101835666</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>72.09438675770339</v>
+        <v>11.7153378481268</v>
       </c>
       <c r="D12" t="n">
-        <v>72.0402999074754</v>
+        <v>11.70654873496475</v>
       </c>
       <c r="E12" t="n">
-        <v>16.24112554593532</v>
+        <v>2.63918290121449</v>
       </c>
       <c r="F12" t="n">
-        <v>16.50123754975794</v>
+        <v>2.681451101835666</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>57.62797090509374</v>
+        <v>9.364545272077732</v>
       </c>
       <c r="D13" t="n">
-        <v>57.3620448133826</v>
+        <v>9.321332282174673</v>
       </c>
       <c r="E13" t="n">
-        <v>16.24112554593532</v>
+        <v>2.63918290121449</v>
       </c>
       <c r="F13" t="n">
-        <v>16.50123754975794</v>
+        <v>2.681451101835666</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>26.92382501794099</v>
+        <v>4.375121565415411</v>
       </c>
       <c r="D14" t="n">
-        <v>52.25035434560208</v>
+        <v>8.490682581160337</v>
       </c>
       <c r="E14" t="n">
-        <v>16.24112554593532</v>
+        <v>2.63918290121449</v>
       </c>
       <c r="F14" t="n">
-        <v>16.50123754975794</v>
+        <v>2.681451101835666</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>49.59115333823276</v>
+        <v>8.058562417462825</v>
       </c>
       <c r="D15" t="n">
-        <v>47.8923395771934</v>
+        <v>7.782505181293927</v>
       </c>
       <c r="E15" t="n">
-        <v>16.24112554593532</v>
+        <v>2.63918290121449</v>
       </c>
       <c r="F15" t="n">
-        <v>16.50123754975794</v>
+        <v>2.681451101835666</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>52.81631313630049</v>
+        <v>8.58265088464883</v>
       </c>
       <c r="D16" t="n">
-        <v>51.39132485740977</v>
+        <v>8.351090289329088</v>
       </c>
       <c r="E16" t="n">
-        <v>16.24112554593532</v>
+        <v>2.63918290121449</v>
       </c>
       <c r="F16" t="n">
-        <v>16.50123754975794</v>
+        <v>2.681451101835666</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>44.51790595498942</v>
+        <v>7.23415971768578</v>
       </c>
       <c r="D17" t="n">
-        <v>55.2648089394088</v>
+        <v>8.980531452653931</v>
       </c>
       <c r="E17" t="n">
-        <v>16.24112554593532</v>
+        <v>2.63918290121449</v>
       </c>
       <c r="F17" t="n">
-        <v>16.50123754975794</v>
+        <v>2.681451101835666</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
